--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104546_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104546_W10.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2944</v>
+        <v>6.8582</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8924</v>
+        <v>5.2052</v>
       </c>
       <c r="F2" t="n">
-        <v>1.402</v>
+        <v>1.653</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0043</v>
+        <v>1.9962</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7892</v>
+        <v>-0.7952</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7935</v>
+        <v>2.7915</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7686</v>
+        <v>1.735</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.1021</v>
+        <v>-1.1246</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8707</v>
+        <v>2.8596</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2356</v>
+        <v>0.2613</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3129</v>
+        <v>0.3294</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0293</v>
+        <v>0.5448</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1542</v>
+        <v>0.2018</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1249</v>
+        <v>0.343</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W2" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9963</v>
+        <v>6.2237</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1075</v>
+        <v>2.02</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8887</v>
+        <v>4.2037</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6976</v>
+        <v>4.694</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7416</v>
+        <v>1.7433</v>
       </c>
       <c r="I3" t="n">
-        <v>2.956</v>
+        <v>2.9507</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7721</v>
+        <v>2.7404</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7997</v>
+        <v>0.7822</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9724</v>
+        <v>1.9582</v>
       </c>
       <c r="M3" t="n">
-        <v>1.9256</v>
+        <v>1.9536</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9419</v>
+        <v>0.9611</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>0.206</v>
+        <v>0.4403</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5111</v>
+        <v>0.4665</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3052</v>
+        <v>-0.0262</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8289</v>
+        <v>5.3799</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3464</v>
+        <v>5.1473</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4825</v>
+        <v>0.2326</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9042</v>
+        <v>1.6274</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8269</v>
+        <v>0.8698</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.7577</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2987</v>
+        <v>3.877</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2614</v>
+        <v>1.5168</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>2.3602</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6055</v>
+        <v>-2.2496</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5655</v>
+        <v>-0.6471</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04</v>
+        <v>-1.6025</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.764</v>
+        <v>0.6143</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4748</v>
+        <v>0.1808</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2891</v>
+        <v>0.4335</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8047</v>
+        <v>4.5875</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6338</v>
+        <v>2.2751</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1709</v>
+        <v>2.3124</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6315</v>
+        <v>2.9001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8613</v>
+        <v>2.818</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7702</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>3.904</v>
+        <v>2.2813</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5239</v>
+        <v>2.244</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3802</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2725</v>
+        <v>0.6189</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6626</v>
+        <v>0.574</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.6099</v>
+        <v>0.0449</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.039</v>
+        <v>0.5296</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3629</v>
+        <v>0.4294</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4019</v>
+        <v>0.1002</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.54</v>
+        <v>3.9172</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5676</v>
+        <v>3.3155</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9724</v>
+        <v>0.6017</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6981</v>
+        <v>3.708</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5439</v>
+        <v>2.5473</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1542</v>
+        <v>1.1607</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6175</v>
+        <v>2.6006</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7592</v>
+        <v>1.7442</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0806</v>
+        <v>1.1074</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7847</v>
+        <v>0.8032</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3468</v>
+        <v>0.7052</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7894</v>
+        <v>0.5571</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5574</v>
+        <v>0.1481</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5293</v>
+        <v>3.5098</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1325</v>
+        <v>1.9871</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3968</v>
+        <v>1.5227</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9201</v>
+        <v>0.9163</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2613</v>
+        <v>1.2527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3411</v>
+        <v>-0.3364</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8845</v>
+        <v>0.855</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7753</v>
+        <v>0.7509</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1092</v>
+        <v>0.104</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0356</v>
+        <v>0.0613</v>
       </c>
       <c r="N7" t="n">
-        <v>0.486</v>
+        <v>0.5018</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2482</v>
+        <v>1.2277</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7017</v>
+        <v>0.5874</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5465</v>
+        <v>0.6404</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2175</v>
+        <v>2.7573</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2392</v>
+        <v>3.0958</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0216</v>
+        <v>-0.3386</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6443</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0692</v>
+        <v>2.068</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.7135</v>
+        <v>-2.7157</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7892</v>
+        <v>0.7677</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9914</v>
+        <v>1.9822</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2023</v>
+        <v>-1.2146</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4335</v>
+        <v>-1.4154</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0857</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3401</v>
+        <v>0.8814</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6503</v>
+        <v>0.5362</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6899</v>
+        <v>0.3452</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.5833</v>
+        <v>2.6142</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7726</v>
+        <v>-0.276</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8107</v>
+        <v>2.8902</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0268</v>
+        <v>3.9519</v>
       </c>
       <c r="H9" t="n">
-        <v>2.658</v>
+        <v>4.6414</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6312</v>
+        <v>-0.6895</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2712</v>
+        <v>2.7694</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2339</v>
+        <v>3.1199</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0373</v>
+        <v>-0.3505</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2444</v>
+        <v>1.1825</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4241</v>
+        <v>1.5215</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6685</v>
+        <v>-0.3391</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-5.6908</v>
       </c>
       <c r="R9" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1689</v>
+        <v>0.3531</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4748</v>
+        <v>0.4665</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.3117</v>
+        <v>2.0785</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1117</v>
+        <v>1.4032</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4234</v>
+        <v>0.6752</v>
       </c>
       <c r="G10" t="n">
-        <v>3.9505</v>
+        <v>1.0322</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6435</v>
+        <v>2.654</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-1.6218</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7931</v>
+        <v>2.2608</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1343</v>
+        <v>2.2236</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.3413</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1574</v>
+        <v>-1.2285</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5091</v>
+        <v>0.4305</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3517</v>
+        <v>-1.659</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.8562</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.6708</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0321</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5807</v>
+        <v>0.1228</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5486</v>
+        <v>0.538</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7107</v>
+        <v>0.9902</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2858</v>
+        <v>1.401</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.4108</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2121</v>
+        <v>0.2152</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4638</v>
+        <v>0.4648</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3554</v>
+        <v>1.3522</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6795</v>
+        <v>-0.6722</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1255</v>
+        <v>0.129</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0348</v>
+        <v>0.3101</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1043</v>
+        <v>0.2614</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1371</v>
+        <v>-1.1786</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2149</v>
+        <v>-2.4091</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0778</v>
+        <v>1.2305</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.0363</v>
+        <v>-4.0475</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3131</v>
+        <v>2.3121</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.3494</v>
+        <v>-6.3596</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4297</v>
+        <v>-2.4598</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2512</v>
+        <v>2.2408</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.6808</v>
+        <v>-4.7006</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6066</v>
+        <v>-1.5877</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1403</v>
+        <v>-0.1813</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2148</v>
+        <v>0.0507</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3551</v>
+        <v>-0.232</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="13">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6003</v>
+        <v>-3.3154</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7679</v>
+        <v>-3.2561</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1677</v>
+        <v>-0.0593</v>
       </c>
       <c r="G13" t="n">
-        <v>-6.1588</v>
+        <v>-6.1721</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.4358</v>
+        <v>-0.4365</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.723</v>
+        <v>-5.7356</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.5657</v>
+        <v>-3.5947</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0417</v>
+        <v>-0.0485</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.524</v>
+        <v>-3.5463</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.593</v>
+        <v>-2.5774</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3563</v>
+        <v>0.6502</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3629</v>
+        <v>0.1808</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7192</v>
+        <v>0.4694</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>34.07940000000001</v>
+        <v>34.4225</v>
       </c>
       <c r="E14" t="n">
-        <v>19.8833</v>
+        <v>19.909</v>
       </c>
       <c r="F14" t="n">
-        <v>14.1962</v>
+        <v>14.5133</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6696</v>
+        <v>10.6388</v>
       </c>
       <c r="H14" t="n">
-        <v>19.9059</v>
+        <v>19.8901</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.2362</v>
+        <v>-9.251099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>15.4589</v>
+        <v>15.1849</v>
       </c>
       <c r="K14" t="n">
-        <v>15.6731</v>
+        <v>15.5177</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2141999999999999</v>
+        <v>-0.3331000000000004</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.7892</v>
+        <v>-4.5458</v>
       </c>
       <c r="N14" t="n">
-        <v>4.232799999999999</v>
+        <v>4.3723</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.021899999999999</v>
+        <v>-8.918099999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>9.0733</v>
+        <v>9.105399999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R14" t="n">
-        <v>19.2808</v>
+        <v>19.3488</v>
       </c>
       <c r="S14" t="n">
-        <v>6.3666</v>
+        <v>6.7362</v>
       </c>
       <c r="T14" t="n">
-        <v>3.448</v>
+        <v>3.8287</v>
       </c>
       <c r="U14" t="n">
-        <v>2.918399999999999</v>
+        <v>2.9077</v>
       </c>
       <c r="V14" t="n">
-        <v>7.9702</v>
+        <v>7.9419</v>
       </c>
       <c r="W14" t="n">
-        <v>11.1839</v>
+        <v>11.1389</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2138</v>
+        <v>-3.196999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>M. HUGHES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0776</v>
+        <v>1.6365</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2193</v>
+        <v>4.3267</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1416</v>
+        <v>-2.6902</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.2906</v>
+        <v>3.6608</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6159</v>
+        <v>-1.1581</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3253</v>
+        <v>4.8189</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0196</v>
+        <v>4.8497</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.167</v>
+        <v>0.1207</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>4.7291</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3103</v>
+        <v>-1.189</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4489</v>
+        <v>-1.2788</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1387</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9561</v>
+        <v>-0.2126</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2411</v>
+        <v>-0.523</v>
       </c>
       <c r="U15" t="n">
-        <v>0.715</v>
+        <v>0.3104</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>-2.4945</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HUGHES</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.705</v>
+        <v>0.4509</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7475</v>
+        <v>0.5379</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0424</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6488</v>
+        <v>-1.298</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1704</v>
+        <v>-1.6305</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8193</v>
+        <v>0.3325</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8604</v>
+        <v>-0.0076</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1212</v>
+        <v>-0.1938</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7392</v>
+        <v>0.1862</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2116</v>
+        <v>-1.2904</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2917</v>
+        <v>-1.4367</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>0.1463</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1175</v>
+        <v>1.3424</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.113</v>
+        <v>0.5942</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0046</v>
+        <v>0.7482</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.5068</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.5068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5704</v>
+        <v>-0.2156</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3476</v>
+        <v>-1.0039</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7772</v>
+        <v>0.7883</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2251</v>
+        <v>-0.2241</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0648</v>
+        <v>0.0577</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.039</v>
+        <v>-1.0342</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7864</v>
+        <v>0.7896</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1391</v>
+        <v>0.4947</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2782</v>
+        <v>0.0765</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4174</v>
+        <v>0.4182</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8054</v>
+        <v>-0.5818</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9727</v>
+        <v>-0.75</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1672</v>
+        <v>0.1682</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7421</v>
+        <v>0.7531</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3449</v>
+        <v>1.146</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3972</v>
+        <v>-0.393</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6944</v>
+        <v>1.5107</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0173</v>
+        <v>1.3617</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7117</v>
+        <v>0.1489</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0477</v>
+        <v>-0.7576000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3622</v>
+        <v>-0.2157</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3145</v>
+        <v>-0.5419</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1294</v>
+        <v>-0.1057</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2782</v>
+        <v>-0.3485</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1488</v>
+        <v>0.2429</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-0.7739</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9284</v>
+        <v>-0.8642</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.7359</v>
+        <v>-0.9767</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1925</v>
+        <v>0.1126</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7474</v>
+        <v>-0.7413</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1472</v>
+        <v>-0.3419</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3998</v>
+        <v>-0.3993</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5173</v>
+        <v>-0.6979</v>
       </c>
       <c r="K19" t="n">
-        <v>1.368</v>
+        <v>0.0172</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1493</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7699</v>
+        <v>-0.0433</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.3592</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.549</v>
+        <v>0.3159</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4509</v>
+        <v>-0.1928</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3478</v>
+        <v>-0.2788</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1031</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7712</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7458</v>
+        <v>-1.8341</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1175</v>
+        <v>-0.549</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6283</v>
+        <v>-1.2852</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2161</v>
+        <v>-1.2149</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2236</v>
+        <v>-2.2203</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0076</v>
+        <v>1.0054</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0045</v>
+        <v>-0.0259</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9415</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2116</v>
+        <v>-1.189</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O20" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1175</v>
+        <v>-0.2126</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.113</v>
+        <v>-0.523</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0046</v>
+        <v>0.3104</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2406</v>
+        <v>-2.6937</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8632</v>
+        <v>-2.6693</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3774</v>
+        <v>-0.0244</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.8286</v>
       </c>
       <c r="H21" t="n">
-        <v>-6.1052</v>
+        <v>-6.1033</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2751</v>
+        <v>5.2747</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8659</v>
+        <v>0.8339</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.7586</v>
+        <v>-3.7758</v>
       </c>
       <c r="L21" t="n">
-        <v>4.6246</v>
+        <v>4.6097</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.696</v>
+        <v>-1.6624</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3466</v>
+        <v>-2.3274</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1422</v>
+        <v>0.4112</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3266</v>
+        <v>-0.0887</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1845</v>
+        <v>0.4999</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.8159</v>
+        <v>-3.9269</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0761</v>
+        <v>-1.2356</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7399</v>
+        <v>-2.6913</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.477</v>
+        <v>-2.4748</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2611</v>
+        <v>-2.2604</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.415</v>
+        <v>-1.4454</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9218</v>
+        <v>-0.9383</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.062</v>
+        <v>-1.0295</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3393</v>
+        <v>-1.3221</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6338</v>
+        <v>-0.748</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3266</v>
+        <v>-0.4441</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3072</v>
+        <v>-0.3039</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="23">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1047</v>
+        <v>-3.9738</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3622</v>
+        <v>-1.4021</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.7425</v>
+        <v>-2.5717</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.501</v>
+        <v>-0.5034</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5223</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0213</v>
+        <v>0.0193</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2328</v>
+        <v>1.1998</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6438</v>
+        <v>0.627</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7338</v>
+        <v>-1.7032</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1662</v>
+        <v>-1.1497</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6698</v>
+        <v>-0.5402</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3266</v>
+        <v>-0.3256</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3432</v>
+        <v>-0.2146</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8849</v>
+        <v>-5.0682</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9952</v>
+        <v>-4.0113</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8897</v>
+        <v>-1.0569</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.796</v>
+        <v>-3.6418</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3376</v>
+        <v>-1.6426</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4584</v>
+        <v>-1.9992</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.3208</v>
+        <v>-1.191</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.6837</v>
+        <v>-0.1626</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6371</v>
+        <v>-1.0284</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4752</v>
+        <v>-2.4508</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6539</v>
+        <v>-1.48</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1787</v>
+        <v>-0.9708</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9962</v>
+        <v>0.2565</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4597</v>
+        <v>-0.544</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.456</v>
+        <v>0.8005</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.9897</v>
+        <v>-5.4312</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6786</v>
+        <v>-3.4853</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3111</v>
+        <v>-1.9459</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.6356</v>
+        <v>-3.7841</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.6391</v>
+        <v>-3.3346</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9965</v>
+        <v>-0.4495</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.1582</v>
+        <v>-2.3374</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1425</v>
+        <v>-1.6967</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.0157</v>
+        <v>-0.6407</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4774</v>
+        <v>-1.4467</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.4966</v>
+        <v>-1.638</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9808</v>
+        <v>0.1912</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6735</v>
+        <v>-0.5576</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.2521</v>
+        <v>-0.0097</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5786</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.7763</v>
+        <v>-6.0443</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0141</v>
+        <v>-3.2947</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.7622</v>
+        <v>-2.7495</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3895</v>
+        <v>-0.3789</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.6076</v>
+        <v>-1.5974</v>
       </c>
       <c r="I26" t="n">
-        <v>1.2181</v>
+        <v>1.2185</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8211</v>
+        <v>1.7994</v>
       </c>
       <c r="K26" t="n">
-        <v>0.4085</v>
+        <v>0.3997</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.2106</v>
+        <v>-2.1783</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.0161</v>
+        <v>-1.9971</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R26" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5307</v>
+        <v>-0.7956</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2571</v>
+        <v>-0.4928</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2736</v>
+        <v>-0.3028</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-34.0795</v>
+        <v>-28.5464</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.1963</v>
+        <v>-14.5133</v>
       </c>
       <c r="F27" t="n">
-        <v>-19.8832</v>
+        <v>-14.0329</v>
       </c>
       <c r="G27" t="n">
-        <v>-10.6696</v>
+        <v>-10.6387</v>
       </c>
       <c r="H27" t="n">
-        <v>-19.9056</v>
+        <v>-19.8899</v>
       </c>
       <c r="I27" t="n">
-        <v>9.236200000000002</v>
+        <v>9.251099999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>4.789</v>
+        <v>4.546</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.232899999999999</v>
+        <v>-4.3723</v>
       </c>
       <c r="L27" t="n">
-        <v>9.022000000000002</v>
+        <v>8.918200000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>-15.4587</v>
+        <v>-15.1848</v>
       </c>
       <c r="N27" t="n">
-        <v>-15.6731</v>
+        <v>-15.5177</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2141999999999999</v>
+        <v>0.3329000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>-9.073399999999999</v>
+        <v>-9.105400000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>-19.2809</v>
+        <v>-19.3489</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2076</v>
+        <v>10.2436</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.366299999999999</v>
+        <v>-0.8603000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.9184</v>
+        <v>-2.9075</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.448</v>
+        <v>2.0473</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.9701</v>
+        <v>-7.9418</v>
       </c>
       <c r="W27" t="n">
-        <v>3.2139</v>
+        <v>3.1971</v>
       </c>
       <c r="X27" t="n">
-        <v>-11.184</v>
+        <v>-11.1389</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104546_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104546_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.196999999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104546_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-11.1389</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
